--- a/docs/downloads/05/tbl_latrine_alaotra_ambohidrony.xlsx
+++ b/docs/downloads/05/tbl_latrine_alaotra_ambohidrony.xlsx
@@ -441,12 +441,6 @@
           <t>Fosse septique en individuel</t>
         </is>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1.9</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -513,12 +507,6 @@
           <t>Fosse septique en commun</t>
         </is>
       </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-      <c r="D9">
-        <v>0.6</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -530,12 +518,6 @@
         <is>
           <t>Fosse septique en individuel</t>
         </is>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <v>0.6</v>
       </c>
     </row>
   </sheetData>
